--- a/Solar Power.xlsx
+++ b/Solar Power.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/electricity application/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF109427-2657-564E-9A4C-C83C473D94EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4AD010-1DE8-564D-9344-F89B04D13F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="126">
   <si>
     <t>Metrics</t>
   </si>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>Production</t>
+  </si>
+  <si>
+    <t>Spatial requirement</t>
   </si>
 </sst>
 </file>
@@ -2779,7 +2782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5344E307-70EA-9749-BC3D-54A83804696F}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
@@ -3124,6 +3127,29 @@
       </c>
       <c r="G14">
         <v>0.91825292799460578</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15">
+        <v>88</v>
+      </c>
+      <c r="C15">
+        <v>177</v>
+      </c>
+      <c r="D15">
+        <v>2837</v>
+      </c>
+      <c r="E15">
+        <v>5674</v>
+      </c>
+      <c r="F15">
+        <v>28370</v>
+      </c>
+      <c r="G15">
+        <v>56739</v>
       </c>
     </row>
   </sheetData>
@@ -5530,22 +5556,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="F19:G19"/>
@@ -5555,6 +5565,22 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F64:G64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
